--- a/Accounting/Cash+Flow+Statement_pre-solution.xlsx
+++ b/Accounting/Cash+Flow+Statement_pre-solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365dsc-my.sharepoint.com/personal/team_365dsc_onmicrosoft_com/Documents/Courses/365 Financial Analyst/Accounting and Financial Statement Analysis/To Tony/Videos/5.8 Cash flow in practice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Financial-Analysis\Accounting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="11_8EC9C173222AB045CA43E9001FD2681260F98D4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F02ADC2-F47C-4531-9E48-20D0F99E6D00}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B492CD0-ED15-4703-BA97-D577ADCF2902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P&amp;L" sheetId="21" r:id="rId1"/>
@@ -349,7 +349,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -365,9 +365,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -715,28 +712,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="B1:D20"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" style="1" customWidth="1"/>
     <col min="3" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.21875" style="1"/>
+    <col min="5" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="12" x14ac:dyDescent="0.25">
-      <c r="C3" s="14">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C3" s="13">
         <v>2020</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>2021</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -747,156 +744,156 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>13759.999999999998</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <v>16581.620906666667</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <v>-7502.2966666666662</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>-8334.1953394114335</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>6257.703333333332</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>8247.4255672552335</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>-2711</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <v>-2988.0355991937986</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>3546.703333333332</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>5259.389968061435</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <v>-233.9296875</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>-328.08914935226204</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>3312.773645833332</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <v>4931.3008187091727</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>-10</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>-15</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <f>SUM(C11:C12)</f>
         <v>3302.773645833332</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>4916.3008187091727</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <f>-0.15*C13</f>
         <v>-495.41604687499978</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>-737.44512280637593</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>0.15</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <f>C13+C14</f>
         <v>2807.3575989583323</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>4178.8556959027965</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -909,189 +906,189 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="B1:G20"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.21875" style="1"/>
+    <col min="2" max="2" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="2:7" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:7" ht="12" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>3418</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <f>6900.4+90+200+500-964</f>
         <v>6726.4</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>35.200000000000003</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>70.194725131782945</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>776.66666666666652</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <v>935.92966842377257</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>420</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <v>882</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>1454.0703125</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="18">
         <v>1955.0622084810716</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <f>SUM(C5:C9)</f>
         <v>6103.9369791666668</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <f>SUM(D5:D9)</f>
         <v>10569.586602036627</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>257.43925925925919</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <v>284.73662656076658</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>0</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>672</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="18">
         <v>1040</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>159</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="18">
         <v>302</v>
       </c>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <v>5015.8575989583323</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="18">
         <v>8943</v>
       </c>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="2:5" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <f>SUM(C12:C16)</f>
         <v>6104.2968582175918</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <f>SUM(D12:D16)</f>
         <v>10569.736626560767</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
@@ -1105,22 +1102,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="B1:F32"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.21875" style="1"/>
+    <col min="2" max="2" width="30.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.08984375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C3" s="13">
         <v>2020</v>
       </c>
@@ -1128,7 +1125,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1139,230 +1136,269 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <v>2738.93</v>
       </c>
-      <c r="D5" s="28"/>
-    </row>
-    <row r="6" spans="2:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-    </row>
-    <row r="7" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="27">
+        <f>'P&amp;L'!D9</f>
+        <v>5259.389968061435</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+    </row>
+    <row r="7" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <f>'P&amp;L'!C12</f>
         <v>-10</v>
       </c>
-      <c r="D7" s="29"/>
-    </row>
-    <row r="8" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="28">
+        <f>'P&amp;L'!D12</f>
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <v>-393.80981249999996</v>
       </c>
-      <c r="D8" s="29"/>
-    </row>
-    <row r="9" spans="2:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D8" s="28">
+        <f>'P&amp;L'!D14</f>
+        <v>-737.44512280637593</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <v>-99.199999999999989</v>
       </c>
-      <c r="D10" s="29"/>
-      <c r="F10" s="32"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D10" s="28">
+        <f>-(BS!D6-BS!C6)</f>
+        <v>-34.994725131782943</v>
+      </c>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <v>-990</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="F11" s="32"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D11" s="28">
+        <f>-(BS!D7-BS!C7)</f>
+        <v>-159.26300175710605</v>
+      </c>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <v>262.13555555555564</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="F12" s="32"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D12" s="28">
+        <f>BS!D12-BS!C12</f>
+        <v>27.297367301507393</v>
+      </c>
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <v>-41</v>
       </c>
-      <c r="D14" s="29"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D14" s="28">
+        <f>-(BS!D8-BS!C8)</f>
+        <v>-462</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <v>-87</v>
       </c>
-      <c r="D15" s="29"/>
-    </row>
-    <row r="16" spans="2:6" ht="12" x14ac:dyDescent="0.25">
+      <c r="D15" s="28">
+        <f>BS!D14-BS!C14</f>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <f>SUM(C5:C15)</f>
         <v>1380.0557430555555</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <f>SUM(D5:D15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+        <v>4245.9844856676773</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="28">
         <v>-474</v>
       </c>
-      <c r="D18" s="29"/>
-    </row>
-    <row r="19" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+      <c r="D18" s="28">
+        <f>-(BS!D9-BS!C9-'P&amp;L'!D10)</f>
+        <v>-829.08104533333358</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <f>SUM(C18)</f>
         <v>-474</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <f>SUM(D18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+        <v>-829.08104533333358</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="28">
         <v>43</v>
       </c>
-      <c r="D21" s="29"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D21" s="28">
+        <f>BS!D15-BS!C15</f>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="28">
         <v>-580</v>
       </c>
-      <c r="D22" s="29"/>
-    </row>
-    <row r="23" spans="2:4" ht="12" x14ac:dyDescent="0.25">
+      <c r="D22" s="28">
+        <f>BS!D16-BS!C16-'P&amp;L'!D16</f>
+        <v>-251.71329486112882</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="29">
         <f>SUM(C21:C22)</f>
         <v>-537</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <f>D21+D22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-    </row>
-    <row r="25" spans="2:4" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-    </row>
-    <row r="26" spans="2:4" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-108.71329486112882</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+    </row>
+    <row r="25" spans="2:4" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+    </row>
+    <row r="26" spans="2:4" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <f>C16+C19+C23</f>
         <v>369.05574305555547</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="30">
         <f>D23+D19+D16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+        <v>3308.1901454732151</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="28">
         <v>3049</v>
       </c>
-      <c r="D28" s="29"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D28" s="28">
+        <f>C29</f>
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="28">
         <f>BS!C5</f>
         <v>3418</v>
       </c>
-      <c r="D29" s="29"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-    </row>
-    <row r="31" spans="2:4" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="28">
+        <f>BS!D5</f>
+        <v>6726.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+    </row>
+    <row r="31" spans="2:4" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="30">
         <f>C29-C28</f>
         <v>369</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="30">
         <f>D29-D28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>3308.3999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
